--- a/promotion/viid_pid/viid_pid확인.xlsx
+++ b/promotion/viid_pid/viid_pid확인.xlsx
@@ -29,15 +29,6 @@
     <t>SKU ID</t>
   </si>
   <si>
-    <t>벤더아이템 ID</t>
-  </si>
-  <si>
-    <t>Product ID</t>
-  </si>
-  <si>
-    <t>제품명</t>
-  </si>
-  <si>
     <t>오아클린이워터B-UV-포그밀크</t>
   </si>
   <si>
@@ -1629,13 +1620,37 @@
   </si>
   <si>
     <t>오아에어스트레이트-베이지</t>
+  </si>
+  <si>
+    <t>viid</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>pid</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>sku</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>명</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1662,6 +1677,13 @@
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="4">
@@ -2044,13 +2066,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>532</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>533</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>3</v>
+        <v>534</v>
       </c>
       <c r="E1" s="3"/>
     </row>
@@ -2065,7 +2087,7 @@
         <v>9369413253</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -2080,7 +2102,7 @@
         <v>9369413253</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E3" s="3"/>
     </row>
@@ -2095,7 +2117,7 @@
         <v>9369413253</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E4" s="3"/>
     </row>
@@ -2110,7 +2132,7 @@
         <v>2111955991</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E5" s="3"/>
     </row>
@@ -2125,7 +2147,7 @@
         <v>2111956087</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E6" s="3"/>
     </row>
@@ -2140,7 +2162,7 @@
         <v>2373462019</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E7" s="3"/>
     </row>
@@ -2155,7 +2177,7 @@
         <v>7650908643</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2170,7 +2192,7 @@
         <v>8539492067</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E9" s="3"/>
     </row>
@@ -2185,7 +2207,7 @@
         <v>9540070050</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E10" s="3"/>
     </row>
@@ -2200,7 +2222,7 @@
         <v>8312074415</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E11" s="3"/>
     </row>
@@ -2215,7 +2237,7 @@
         <v>7487757176</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E12" s="3"/>
     </row>
@@ -2230,7 +2252,7 @@
         <v>8523156974</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E13" s="3"/>
     </row>
@@ -2245,7 +2267,7 @@
         <v>2309199830</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E14" s="3"/>
     </row>
@@ -2260,7 +2282,7 @@
         <v>2309199830</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E15" s="3"/>
     </row>
@@ -2275,7 +2297,7 @@
         <v>2309199830</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E16" s="3"/>
     </row>
@@ -2290,7 +2312,7 @@
         <v>8605113448</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E17" s="3"/>
     </row>
@@ -2305,7 +2327,7 @@
         <v>8605113448</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E18" s="3"/>
     </row>
@@ -2320,7 +2342,7 @@
         <v>2309199830</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E19" s="3"/>
     </row>
@@ -2335,7 +2357,7 @@
         <v>2309199830</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E20" s="3"/>
     </row>
@@ -2350,7 +2372,7 @@
         <v>2032761500</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E21" s="3"/>
     </row>
@@ -2365,7 +2387,7 @@
         <v>2032761500</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E22" s="3"/>
     </row>
@@ -2380,7 +2402,7 @@
         <v>8248127797</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E23" s="3"/>
     </row>
@@ -2395,7 +2417,7 @@
         <v>8248127797</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E24" s="3"/>
     </row>
@@ -2410,7 +2432,7 @@
         <v>8909198664</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E25" s="3"/>
     </row>
@@ -2425,7 +2447,7 @@
         <v>8909198664</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E26" s="3"/>
     </row>
@@ -2440,7 +2462,7 @@
         <v>9519863284</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E27" s="3"/>
     </row>
@@ -2455,7 +2477,7 @@
         <v>9519863284</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E28" s="3"/>
     </row>
@@ -2470,7 +2492,7 @@
         <v>8909180728</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E29" s="3"/>
     </row>
@@ -2485,7 +2507,7 @@
         <v>5884429000</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E30" s="3"/>
     </row>
@@ -2500,7 +2522,7 @@
         <v>4796437606</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E31" s="3"/>
     </row>
@@ -2515,7 +2537,7 @@
         <v>4796437606</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E32" s="3"/>
     </row>
@@ -2530,7 +2552,7 @@
         <v>4925766300</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E33" s="3"/>
     </row>
@@ -2545,7 +2567,7 @@
         <v>6559459406</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E34" s="3"/>
     </row>
@@ -2560,7 +2582,7 @@
         <v>6559459406</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E35" s="3"/>
     </row>
@@ -2575,7 +2597,7 @@
         <v>1929721801</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E36" s="3"/>
     </row>
@@ -2590,7 +2612,7 @@
         <v>9320197885</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E37" s="3"/>
     </row>
@@ -2605,7 +2627,7 @@
         <v>9320197885</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E38" s="3"/>
     </row>
@@ -2620,7 +2642,7 @@
         <v>9320197885</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E39" s="3"/>
     </row>
@@ -2635,7 +2657,7 @@
         <v>6723272601</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E40" s="3"/>
     </row>
@@ -2650,7 +2672,7 @@
         <v>7314997062</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E41" s="3"/>
     </row>
@@ -2665,7 +2687,7 @@
         <v>8457639663</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E42" s="3"/>
     </row>
@@ -2680,7 +2702,7 @@
         <v>8805227371</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E43" s="3"/>
     </row>
@@ -2695,7 +2717,7 @@
         <v>8924237824</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E44" s="3"/>
     </row>
@@ -2710,7 +2732,7 @@
         <v>9034065016</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E45" s="3"/>
     </row>
@@ -2725,7 +2747,7 @@
         <v>9034065016</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E46" s="3"/>
     </row>
@@ -2740,7 +2762,7 @@
         <v>8223026888</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E47" s="3"/>
     </row>
@@ -2755,7 +2777,7 @@
         <v>305643272</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E48" s="3"/>
     </row>
@@ -2770,7 +2792,7 @@
         <v>8769394111</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E49" s="3"/>
     </row>
@@ -2785,7 +2807,7 @@
         <v>9402653296</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E50" s="3"/>
     </row>
@@ -2800,7 +2822,7 @@
         <v>8957005986</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E51" s="3"/>
     </row>
@@ -2815,7 +2837,7 @@
         <v>9239085766</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E52" s="3"/>
     </row>
@@ -2830,7 +2852,7 @@
         <v>9354818837</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E53" s="3"/>
     </row>
@@ -2845,7 +2867,7 @@
         <v>7675640984</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E54" s="3"/>
     </row>
@@ -2860,7 +2882,7 @@
         <v>1519776763</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E55" s="3"/>
     </row>
@@ -2875,7 +2897,7 @@
         <v>8615051465</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E56" s="3"/>
     </row>
@@ -2890,7 +2912,7 @@
         <v>9034510977</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E57" s="3"/>
     </row>
@@ -2905,7 +2927,7 @@
         <v>8723454926</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E58" s="3"/>
     </row>
@@ -2920,7 +2942,7 @@
         <v>1940659064</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E59" s="3"/>
     </row>
@@ -2935,7 +2957,7 @@
         <v>1940659064</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E60" s="3"/>
     </row>
@@ -2950,7 +2972,7 @@
         <v>9423139068</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E61" s="3"/>
     </row>
@@ -2965,7 +2987,7 @@
         <v>6082441446</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E62" s="3"/>
     </row>
@@ -2980,7 +3002,7 @@
         <v>7465167916</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E63" s="3"/>
     </row>
@@ -2995,7 +3017,7 @@
         <v>8869074123</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E64" s="3"/>
     </row>
@@ -3010,7 +3032,7 @@
         <v>8871713453</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E65" s="3"/>
     </row>
@@ -3025,7 +3047,7 @@
         <v>7989527812</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E66" s="3"/>
     </row>
@@ -3040,7 +3062,7 @@
         <v>7989527812</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E67" s="3"/>
     </row>
@@ -3055,7 +3077,7 @@
         <v>290369000</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E68" s="3"/>
     </row>
@@ -3070,7 +3092,7 @@
         <v>7743811249</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E69" s="3"/>
     </row>
@@ -3085,7 +3107,7 @@
         <v>1879044083</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E70" s="3"/>
     </row>
@@ -3100,7 +3122,7 @@
         <v>6939150085</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E71" s="3"/>
     </row>
@@ -3115,7 +3137,7 @@
         <v>9081199861</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E72" s="3"/>
     </row>
@@ -3130,7 +3152,7 @@
         <v>7619977656</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E73" s="3"/>
     </row>
@@ -3145,7 +3167,7 @@
         <v>4381314697</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E74" s="3"/>
     </row>
@@ -3160,7 +3182,7 @@
         <v>7851755157</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E75" s="3"/>
     </row>
@@ -3175,7 +3197,7 @@
         <v>7418067372</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E76" s="3"/>
     </row>
@@ -3190,7 +3212,7 @@
         <v>8873909909</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E77" s="3"/>
     </row>
@@ -3205,7 +3227,7 @@
         <v>9072156089</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E78" s="3"/>
     </row>
@@ -3220,7 +3242,7 @@
         <v>8873255047</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E79" s="3"/>
     </row>
@@ -3235,7 +3257,7 @@
         <v>9158390141</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E80" s="3"/>
     </row>
@@ -3250,7 +3272,7 @@
         <v>9158390141</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E81" s="3"/>
     </row>
@@ -3265,7 +3287,7 @@
         <v>8123844723</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E82" s="3"/>
     </row>
@@ -3280,7 +3302,7 @@
         <v>8099418544</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E83" s="3"/>
     </row>
@@ -3295,7 +3317,7 @@
         <v>8918595360</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E84" s="3"/>
     </row>
@@ -3310,7 +3332,7 @@
         <v>8918917925</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E85" s="3"/>
     </row>
@@ -3325,7 +3347,7 @@
         <v>9009870233</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E86" s="3"/>
     </row>
@@ -3340,7 +3362,7 @@
         <v>9354808973</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E87" s="3"/>
     </row>
@@ -3355,7 +3377,7 @@
         <v>8461693239</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E88" s="3"/>
     </row>
@@ -3370,7 +3392,7 @@
         <v>8461693239</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E89" s="3"/>
     </row>
@@ -3385,7 +3407,7 @@
         <v>8461693239</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E90" s="3"/>
     </row>
@@ -3400,7 +3422,7 @@
         <v>8461693239</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E91" s="3"/>
     </row>
@@ -3415,7 +3437,7 @@
         <v>8461693239</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E92" s="3"/>
     </row>
@@ -3430,7 +3452,7 @@
         <v>9535222411</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E93" s="3"/>
     </row>
@@ -3445,7 +3467,7 @@
         <v>9535222411</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E94" s="3"/>
     </row>
@@ -3460,7 +3482,7 @@
         <v>9535222411</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E95" s="3"/>
     </row>
@@ -3475,7 +3497,7 @@
         <v>5638515040</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E96" s="3"/>
     </row>
@@ -3490,7 +3512,7 @@
         <v>6703646038</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E97" s="3"/>
     </row>
@@ -3505,7 +3527,7 @@
         <v>63237050</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E98" s="3"/>
     </row>
@@ -3520,7 +3542,7 @@
         <v>8813988641</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E99" s="3"/>
     </row>
@@ -3535,7 +3557,7 @@
         <v>4704568656</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E100" s="3"/>
     </row>
@@ -3550,7 +3572,7 @@
         <v>8885086595</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E101" s="3"/>
     </row>
@@ -3565,7 +3587,7 @@
         <v>124260572</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E102" s="3"/>
     </row>
@@ -3580,7 +3602,7 @@
         <v>7246118706</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E103" s="3"/>
     </row>
@@ -3595,7 +3617,7 @@
         <v>7232383993</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E104" s="3"/>
     </row>
@@ -3610,7 +3632,7 @@
         <v>6359772421</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E105" s="3"/>
     </row>
@@ -3625,7 +3647,7 @@
         <v>7429871332</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E106" s="3"/>
     </row>
@@ -3640,7 +3662,7 @@
         <v>7281509023</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E107" s="3"/>
     </row>
@@ -3655,7 +3677,7 @@
         <v>7776255087</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E108" s="3"/>
     </row>
@@ -3670,7 +3692,7 @@
         <v>8542895508</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E109" s="3"/>
     </row>
@@ -3685,7 +3707,7 @@
         <v>7865837640</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E110" s="3"/>
     </row>
@@ -3700,7 +3722,7 @@
         <v>8202253102</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E111" s="3"/>
     </row>
@@ -3715,7 +3737,7 @@
         <v>9276306216</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E112" s="3"/>
     </row>
@@ -3730,7 +3752,7 @@
         <v>9200664530</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E113" s="3"/>
     </row>
@@ -3745,7 +3767,7 @@
         <v>8405139682</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E114" s="3"/>
     </row>
@@ -3760,7 +3782,7 @@
         <v>8414916363</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E115" s="3"/>
     </row>
@@ -3775,7 +3797,7 @@
         <v>8142274631</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E116" s="3"/>
     </row>
@@ -3790,7 +3812,7 @@
         <v>9006100108</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E117" s="3"/>
     </row>
@@ -3805,7 +3827,7 @@
         <v>9204804428</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E118" s="3"/>
     </row>
@@ -3820,7 +3842,7 @@
         <v>9204804428</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E119" s="3"/>
     </row>
@@ -3835,7 +3857,7 @@
         <v>9204804428</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E120" s="3"/>
     </row>
@@ -3850,7 +3872,7 @@
         <v>9204804428</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E121" s="3"/>
     </row>
@@ -3865,7 +3887,7 @@
         <v>9212264474</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E122" s="3"/>
     </row>
@@ -3880,7 +3902,7 @@
         <v>9212264474</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E123" s="3"/>
     </row>
@@ -3895,7 +3917,7 @@
         <v>9095624764</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E124" s="3"/>
     </row>
@@ -3910,7 +3932,7 @@
         <v>9111048192</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E125" s="3"/>
     </row>
@@ -3925,7 +3947,7 @@
         <v>8151071866</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E126" s="3"/>
     </row>
@@ -3940,7 +3962,7 @@
         <v>1824769228</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E127" s="3"/>
     </row>
@@ -3955,7 +3977,7 @@
         <v>5339270307</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E128" s="3"/>
     </row>
@@ -3970,7 +3992,7 @@
         <v>7736697362</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E129" s="3"/>
     </row>
@@ -3985,7 +4007,7 @@
         <v>7412619428</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E130" s="3"/>
     </row>
@@ -4000,7 +4022,7 @@
         <v>7300196049</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E131" s="3"/>
     </row>
@@ -4015,7 +4037,7 @@
         <v>7455470197</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E132" s="3"/>
     </row>
@@ -4030,7 +4052,7 @@
         <v>47711246</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E133" s="3"/>
     </row>
@@ -4045,7 +4067,7 @@
         <v>47711246</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E134" s="3"/>
     </row>
@@ -4060,7 +4082,7 @@
         <v>7899771659</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E135" s="3"/>
     </row>
@@ -4075,7 +4097,7 @@
         <v>327922605</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E136" s="3"/>
     </row>
@@ -4090,7 +4112,7 @@
         <v>9036966327</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E137" s="3"/>
     </row>
@@ -4105,7 +4127,7 @@
         <v>1294865619</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E138" s="3"/>
     </row>
@@ -4120,7 +4142,7 @@
         <v>8349567796</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E139" s="3"/>
     </row>
@@ -4135,7 +4157,7 @@
         <v>8357626425</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E140" s="3"/>
     </row>
@@ -4150,7 +4172,7 @@
         <v>60973858</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E141" s="3"/>
     </row>
@@ -4165,7 +4187,7 @@
         <v>196871724</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E142" s="3"/>
     </row>
@@ -4180,7 +4202,7 @@
         <v>8873441208</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E143" s="3"/>
     </row>
@@ -4195,7 +4217,7 @@
         <v>4528133384</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E144" s="3"/>
     </row>
@@ -4210,7 +4232,7 @@
         <v>7989575057</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E145" s="3"/>
     </row>
@@ -4225,7 +4247,7 @@
         <v>9200189841</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E146" s="3"/>
     </row>
@@ -4240,7 +4262,7 @@
         <v>8225038048</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E147" s="3"/>
     </row>
@@ -4255,7 +4277,7 @@
         <v>7660195036</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E148" s="3"/>
     </row>
@@ -4270,7 +4292,7 @@
         <v>6096351824</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E149" s="3"/>
     </row>
@@ -4285,7 +4307,7 @@
         <v>8349457672</v>
       </c>
       <c r="D150" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E150" s="3"/>
     </row>
@@ -4300,7 +4322,7 @@
         <v>1172770014</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E151" s="3"/>
     </row>
@@ -4315,7 +4337,7 @@
         <v>2264083450</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E152" s="3"/>
     </row>
@@ -4330,7 +4352,7 @@
         <v>2106682963</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E153" s="3"/>
     </row>
@@ -4345,7 +4367,7 @@
         <v>4735813852</v>
       </c>
       <c r="D154" s="5" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E154" s="3"/>
     </row>
@@ -4360,7 +4382,7 @@
         <v>6079250032</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E155" s="3"/>
     </row>
@@ -4375,7 +4397,7 @@
         <v>8156708436</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E156" s="3"/>
     </row>
@@ -4390,7 +4412,7 @@
         <v>9036708525</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E157" s="3"/>
     </row>
@@ -4405,7 +4427,7 @@
         <v>9036708525</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E158" s="3"/>
     </row>
@@ -4420,7 +4442,7 @@
         <v>8641534866</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E159" s="3"/>
     </row>
@@ -4435,7 +4457,7 @@
         <v>8405162018</v>
       </c>
       <c r="D160" s="5" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E160" s="3"/>
     </row>
@@ -4450,7 +4472,7 @@
         <v>9168000951</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E161" s="3"/>
     </row>
@@ -4465,7 +4487,7 @@
         <v>8436595901</v>
       </c>
       <c r="D162" s="5" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E162" s="3"/>
     </row>
@@ -4480,7 +4502,7 @@
         <v>8551141514</v>
       </c>
       <c r="D163" s="5" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E163" s="3"/>
     </row>
@@ -4495,7 +4517,7 @@
         <v>8776241105</v>
       </c>
       <c r="D164" s="5" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E164" s="3"/>
     </row>
@@ -4510,7 +4532,7 @@
         <v>4841538278</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E165" s="3"/>
     </row>
@@ -4525,7 +4547,7 @@
         <v>2264058432</v>
       </c>
       <c r="D166" s="5" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E166" s="3"/>
     </row>
@@ -4540,7 +4562,7 @@
         <v>7761901383</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E167" s="3"/>
     </row>
@@ -4555,7 +4577,7 @@
         <v>9158134326</v>
       </c>
       <c r="D168" s="5" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E168" s="3"/>
     </row>
@@ -4570,7 +4592,7 @@
         <v>7732723554</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E169" s="3"/>
     </row>
@@ -4585,7 +4607,7 @@
         <v>9243905275</v>
       </c>
       <c r="D170" s="5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E170" s="3"/>
     </row>
@@ -4600,7 +4622,7 @@
         <v>7297223323</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E171" s="3"/>
     </row>
@@ -4615,7 +4637,7 @@
         <v>7546091128</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E172" s="3"/>
     </row>
@@ -4630,7 +4652,7 @@
         <v>9309487631</v>
       </c>
       <c r="D173" s="5" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E173" s="3"/>
     </row>
@@ -4645,7 +4667,7 @@
         <v>9220715616</v>
       </c>
       <c r="D174" s="5" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E174" s="3"/>
     </row>
@@ -4660,7 +4682,7 @@
         <v>115126243</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E175" s="3"/>
     </row>
@@ -4675,7 +4697,7 @@
         <v>8230291250</v>
       </c>
       <c r="D176" s="5" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E176" s="3"/>
     </row>
@@ -4690,7 +4712,7 @@
         <v>320468159</v>
       </c>
       <c r="D177" s="5" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E177" s="3"/>
     </row>
@@ -4705,7 +4727,7 @@
         <v>8220604080</v>
       </c>
       <c r="D178" s="5" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E178" s="3"/>
     </row>
@@ -4720,7 +4742,7 @@
         <v>8202527570</v>
       </c>
       <c r="D179" s="5" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E179" s="3"/>
     </row>
@@ -4735,7 +4757,7 @@
         <v>8440386805</v>
       </c>
       <c r="D180" s="5" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E180" s="3"/>
     </row>
@@ -4750,7 +4772,7 @@
         <v>7414875369</v>
       </c>
       <c r="D181" s="5" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E181" s="3"/>
     </row>
@@ -4765,7 +4787,7 @@
         <v>8797315031</v>
       </c>
       <c r="D182" s="5" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E182" s="3"/>
     </row>
@@ -4780,7 +4802,7 @@
         <v>8797315031</v>
       </c>
       <c r="D183" s="5" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E183" s="3"/>
     </row>
@@ -4795,7 +4817,7 @@
         <v>8128654238</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E184" s="3"/>
     </row>
@@ -4810,7 +4832,7 @@
         <v>5465980612</v>
       </c>
       <c r="D185" s="5" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E185" s="3"/>
     </row>
@@ -4825,7 +4847,7 @@
         <v>8364078626</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E186" s="3"/>
     </row>
@@ -4840,7 +4862,7 @@
         <v>8769302337</v>
       </c>
       <c r="D187" s="5" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E187" s="3"/>
     </row>
@@ -4855,7 +4877,7 @@
         <v>8769302337</v>
       </c>
       <c r="D188" s="5" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E188" s="3"/>
     </row>
@@ -4870,7 +4892,7 @@
         <v>8708230719</v>
       </c>
       <c r="D189" s="5" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E189" s="3"/>
     </row>
@@ -4885,7 +4907,7 @@
         <v>8715018438</v>
       </c>
       <c r="D190" s="5" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E190" s="3"/>
     </row>
@@ -4900,7 +4922,7 @@
         <v>8708280047</v>
       </c>
       <c r="D191" s="5" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E191" s="3"/>
     </row>
@@ -4915,7 +4937,7 @@
         <v>7959229574</v>
       </c>
       <c r="D192" s="5" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E192" s="3"/>
     </row>
@@ -4930,7 +4952,7 @@
         <v>7959229574</v>
       </c>
       <c r="D193" s="5" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E193" s="3"/>
     </row>
@@ -4945,7 +4967,7 @@
         <v>7230741525</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E194" s="3"/>
     </row>
@@ -4960,7 +4982,7 @@
         <v>7230694468</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E195" s="3"/>
     </row>
@@ -4975,7 +4997,7 @@
         <v>8761468138</v>
       </c>
       <c r="D196" s="5" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E196" s="3"/>
     </row>
@@ -4990,7 +5012,7 @@
         <v>8771741412</v>
       </c>
       <c r="D197" s="5" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E197" s="3"/>
     </row>
@@ -5005,7 +5027,7 @@
         <v>7232585980</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E198" s="3"/>
     </row>
@@ -5020,7 +5042,7 @@
         <v>9005449169</v>
       </c>
       <c r="D199" s="5" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="E199" s="3"/>
     </row>
@@ -5035,7 +5057,7 @@
         <v>5353955662</v>
       </c>
       <c r="D200" s="5" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E200" s="3"/>
     </row>
@@ -5050,7 +5072,7 @@
         <v>5353955662</v>
       </c>
       <c r="D201" s="5" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E201" s="3"/>
     </row>
@@ -5065,7 +5087,7 @@
         <v>7293077394</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E202" s="3"/>
     </row>
@@ -5080,7 +5102,7 @@
         <v>8702687537</v>
       </c>
       <c r="D203" s="5" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E203" s="3"/>
     </row>
@@ -5095,7 +5117,7 @@
         <v>6402983601</v>
       </c>
       <c r="D204" s="5" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E204" s="3"/>
     </row>
@@ -5110,7 +5132,7 @@
         <v>6402983601</v>
       </c>
       <c r="D205" s="5" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E205" s="3"/>
     </row>
@@ -5125,7 +5147,7 @@
         <v>7475562420</v>
       </c>
       <c r="D206" s="5" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="E206" s="3"/>
     </row>
@@ -5140,7 +5162,7 @@
         <v>7475562420</v>
       </c>
       <c r="D207" s="5" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E207" s="3"/>
     </row>
@@ -5155,7 +5177,7 @@
         <v>8072361086</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E208" s="3"/>
     </row>
@@ -5170,7 +5192,7 @@
         <v>8763423811</v>
       </c>
       <c r="D209" s="5" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E209" s="3"/>
     </row>
@@ -5185,7 +5207,7 @@
         <v>8036800913</v>
       </c>
       <c r="D210" s="5" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E210" s="3"/>
     </row>
@@ -5200,7 +5222,7 @@
         <v>8017897778</v>
       </c>
       <c r="D211" s="5" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E211" s="3"/>
     </row>
@@ -5215,7 +5237,7 @@
         <v>8773921562</v>
       </c>
       <c r="D212" s="5" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E212" s="3"/>
     </row>
@@ -5230,7 +5252,7 @@
         <v>8049297154</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E213" s="3"/>
     </row>
@@ -5245,7 +5267,7 @@
         <v>8771747089</v>
       </c>
       <c r="D214" s="5" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E214" s="3"/>
     </row>
@@ -5260,7 +5282,7 @@
         <v>8116119385</v>
       </c>
       <c r="D215" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="E215" s="3"/>
     </row>
@@ -5275,7 +5297,7 @@
         <v>8135619353</v>
       </c>
       <c r="D216" s="5" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E216" s="3"/>
     </row>
@@ -5290,7 +5312,7 @@
         <v>8011373522</v>
       </c>
       <c r="D217" s="5" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E217" s="3"/>
     </row>
@@ -5305,7 +5327,7 @@
         <v>6543679955</v>
       </c>
       <c r="D218" s="5" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E218" s="3"/>
     </row>
@@ -5320,7 +5342,7 @@
         <v>6543679955</v>
       </c>
       <c r="D219" s="5" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E219" s="3"/>
     </row>
@@ -5335,7 +5357,7 @@
         <v>7230170927</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E220" s="3"/>
     </row>
@@ -5350,7 +5372,7 @@
         <v>1624376645</v>
       </c>
       <c r="D221" s="5" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E221" s="3"/>
     </row>
@@ -5365,7 +5387,7 @@
         <v>8760824064</v>
       </c>
       <c r="D222" s="5" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E222" s="3"/>
     </row>
@@ -5380,7 +5402,7 @@
         <v>8771613640</v>
       </c>
       <c r="D223" s="5" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E223" s="3"/>
     </row>
@@ -5395,7 +5417,7 @@
         <v>6572010538</v>
       </c>
       <c r="D224" s="5" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E224" s="3"/>
     </row>
@@ -5410,7 +5432,7 @@
         <v>1624376645</v>
       </c>
       <c r="D225" s="5" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E225" s="3"/>
     </row>
@@ -5425,7 +5447,7 @@
         <v>7240859318</v>
       </c>
       <c r="D226" s="5" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E226" s="3"/>
     </row>
@@ -5440,7 +5462,7 @@
         <v>7240859318</v>
       </c>
       <c r="D227" s="5" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E227" s="3"/>
     </row>
@@ -5455,7 +5477,7 @@
         <v>8797153352</v>
       </c>
       <c r="D228" s="5" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E228" s="3"/>
     </row>
@@ -5470,7 +5492,7 @@
         <v>9434581129</v>
       </c>
       <c r="D229" s="5" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E229" s="3"/>
     </row>
@@ -5485,7 +5507,7 @@
         <v>9454681461</v>
       </c>
       <c r="D230" s="5" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E230" s="3"/>
     </row>
@@ -5500,7 +5522,7 @@
         <v>9486966841</v>
       </c>
       <c r="D231" s="5" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="E231" s="3"/>
     </row>
@@ -5515,7 +5537,7 @@
         <v>9454251995</v>
       </c>
       <c r="D232" s="5" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="E232" s="3"/>
     </row>
@@ -5530,7 +5552,7 @@
         <v>9459611361</v>
       </c>
       <c r="D233" s="5" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="E233" s="3"/>
     </row>
@@ -5545,7 +5567,7 @@
         <v>9496061349</v>
       </c>
       <c r="D234" s="5" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="E234" s="3"/>
     </row>
@@ -5560,7 +5582,7 @@
         <v>9500289355</v>
       </c>
       <c r="D235" s="5" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E235" s="3"/>
     </row>
@@ -5575,7 +5597,7 @@
         <v>9517524490</v>
       </c>
       <c r="D236" s="5" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E236" s="3"/>
     </row>
@@ -5590,7 +5612,7 @@
         <v>9517524485</v>
       </c>
       <c r="D237" s="5" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E237" s="3"/>
     </row>
@@ -5605,7 +5627,7 @@
         <v>9517524521</v>
       </c>
       <c r="D238" s="5" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="E238" s="3"/>
     </row>
@@ -5620,7 +5642,7 @@
         <v>9513778250</v>
       </c>
       <c r="D239" s="5" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="E239" s="3"/>
     </row>
@@ -5635,7 +5657,7 @@
         <v>9513446363</v>
       </c>
       <c r="D240" s="5" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="E240" s="3"/>
     </row>
@@ -5650,7 +5672,7 @@
         <v>9513778250</v>
       </c>
       <c r="D241" s="5" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="E241" s="3"/>
     </row>
@@ -5665,7 +5687,7 @@
         <v>9517870232</v>
       </c>
       <c r="D242" s="5" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E242" s="3"/>
     </row>
@@ -5680,7 +5702,7 @@
         <v>9505109890</v>
       </c>
       <c r="D243" s="5" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="E243" s="3"/>
     </row>
@@ -5695,7 +5717,7 @@
         <v>8596102246</v>
       </c>
       <c r="D244" s="3" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E244" s="3"/>
     </row>
@@ -5710,7 +5732,7 @@
         <v>298437144</v>
       </c>
       <c r="D245" s="3" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="E245" s="3"/>
     </row>
@@ -5725,7 +5747,7 @@
         <v>320275775</v>
       </c>
       <c r="D246" s="3" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E246" s="3"/>
     </row>
@@ -5740,7 +5762,7 @@
         <v>7047272650</v>
       </c>
       <c r="D247" s="3" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="E247" s="3"/>
     </row>
@@ -5755,7 +5777,7 @@
         <v>8365283591</v>
       </c>
       <c r="D248" s="5" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="E248" s="3"/>
     </row>
@@ -5770,7 +5792,7 @@
         <v>7554147814</v>
       </c>
       <c r="D249" s="3" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E249" s="3"/>
     </row>
@@ -5785,7 +5807,7 @@
         <v>7619287775</v>
       </c>
       <c r="D250" s="3" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="E250" s="3"/>
     </row>
@@ -5800,7 +5822,7 @@
         <v>7950771730</v>
       </c>
       <c r="D251" s="3" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="E251" s="3"/>
     </row>
@@ -5815,7 +5837,7 @@
         <v>7612794417</v>
       </c>
       <c r="D252" s="3" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E252" s="3"/>
     </row>
@@ -5830,7 +5852,7 @@
         <v>7723807212</v>
       </c>
       <c r="D253" s="5" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="E253" s="3"/>
     </row>
@@ -5845,7 +5867,7 @@
         <v>8688539675</v>
       </c>
       <c r="D254" s="5" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="E254" s="3"/>
     </row>
@@ -5860,7 +5882,7 @@
         <v>9311942498</v>
       </c>
       <c r="D255" s="5" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="E255" s="3"/>
     </row>
@@ -5875,7 +5897,7 @@
         <v>9311942498</v>
       </c>
       <c r="D256" s="5" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="E256" s="3"/>
     </row>
@@ -5890,7 +5912,7 @@
         <v>8003107365</v>
       </c>
       <c r="D257" s="5" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="E257" s="3"/>
     </row>
@@ -5905,7 +5927,7 @@
         <v>8816300880</v>
       </c>
       <c r="D258" s="5" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E258" s="3"/>
     </row>
@@ -5920,7 +5942,7 @@
         <v>8882351710</v>
       </c>
       <c r="D259" s="5" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="E259" s="3"/>
     </row>
@@ -5935,7 +5957,7 @@
         <v>8882351710</v>
       </c>
       <c r="D260" s="5" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="E260" s="3"/>
     </row>
@@ -5950,7 +5972,7 @@
         <v>8926396803</v>
       </c>
       <c r="D261" s="5" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="E261" s="3"/>
     </row>
@@ -5965,7 +5987,7 @@
         <v>8926396803</v>
       </c>
       <c r="D262" s="5" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="E262" s="3"/>
     </row>
@@ -5980,7 +6002,7 @@
         <v>8926396803</v>
       </c>
       <c r="D263" s="5" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="E263" s="3"/>
     </row>
@@ -5995,7 +6017,7 @@
         <v>9039947782</v>
       </c>
       <c r="D264" s="5" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="E264" s="3"/>
     </row>
@@ -6010,7 +6032,7 @@
         <v>9034174049</v>
       </c>
       <c r="D265" s="3" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E265" s="3"/>
     </row>
@@ -6025,7 +6047,7 @@
         <v>9278208833</v>
       </c>
       <c r="D266" s="5" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="E266" s="3"/>
     </row>
@@ -6040,7 +6062,7 @@
         <v>9278208833</v>
       </c>
       <c r="D267" s="5" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E267" s="3"/>
     </row>
@@ -6055,7 +6077,7 @@
         <v>9276229619</v>
       </c>
       <c r="D268" s="5" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="E268" s="3"/>
     </row>
@@ -6070,7 +6092,7 @@
         <v>9074371425</v>
       </c>
       <c r="D269" s="5" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="E269" s="3"/>
     </row>
@@ -6085,7 +6107,7 @@
         <v>9074365199</v>
       </c>
       <c r="D270" s="5" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="E270" s="3"/>
     </row>
@@ -6100,7 +6122,7 @@
         <v>9131669403</v>
       </c>
       <c r="D271" s="5" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="E271" s="3"/>
     </row>
@@ -6115,7 +6137,7 @@
         <v>9333925562</v>
       </c>
       <c r="D272" s="5" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="E272" s="3"/>
     </row>
@@ -6130,7 +6152,7 @@
         <v>9333925562</v>
       </c>
       <c r="D273" s="5" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="E273" s="3"/>
     </row>
@@ -6145,7 +6167,7 @@
         <v>9333925562</v>
       </c>
       <c r="D274" s="5" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="E274" s="3"/>
     </row>
@@ -6160,7 +6182,7 @@
         <v>9400123284</v>
       </c>
       <c r="D275" s="3" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="E275" s="3"/>
     </row>
@@ -6175,7 +6197,7 @@
         <v>9400123284</v>
       </c>
       <c r="D276" s="5" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="E276" s="3"/>
     </row>
@@ -6190,7 +6212,7 @@
         <v>1749080657</v>
       </c>
       <c r="D277" s="5" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="E277" s="3"/>
     </row>
@@ -6205,7 +6227,7 @@
         <v>1749080657</v>
       </c>
       <c r="D278" s="5" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="E278" s="3"/>
     </row>
@@ -6220,7 +6242,7 @@
         <v>8450829294</v>
       </c>
       <c r="D279" s="5" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="E279" s="3"/>
     </row>
@@ -6235,7 +6257,7 @@
         <v>8463318437</v>
       </c>
       <c r="D280" s="5" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="E280" s="3"/>
     </row>
@@ -6250,7 +6272,7 @@
         <v>8539525746</v>
       </c>
       <c r="D281" s="5" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="E281" s="3"/>
     </row>
@@ -6265,7 +6287,7 @@
         <v>2032552888</v>
       </c>
       <c r="D282" s="5" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="E282" s="3"/>
     </row>
@@ -6280,7 +6302,7 @@
         <v>5816025855</v>
       </c>
       <c r="D283" s="5" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="E283" s="3"/>
     </row>
@@ -6295,7 +6317,7 @@
         <v>8800910264</v>
       </c>
       <c r="D284" s="5" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="E284" s="3"/>
     </row>
@@ -6310,7 +6332,7 @@
         <v>6055495331</v>
       </c>
       <c r="D285" s="5" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E285" s="3"/>
     </row>
@@ -6325,7 +6347,7 @@
         <v>8605229544</v>
       </c>
       <c r="D286" s="5" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="E286" s="3"/>
     </row>
@@ -6340,7 +6362,7 @@
         <v>7844631774</v>
       </c>
       <c r="D287" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="E287" s="3"/>
     </row>
@@ -6355,7 +6377,7 @@
         <v>4931399316</v>
       </c>
       <c r="D288" s="5" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="E288" s="3"/>
     </row>
@@ -6370,7 +6392,7 @@
         <v>5142485634</v>
       </c>
       <c r="D289" s="5" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E289" s="3"/>
     </row>
@@ -6385,7 +6407,7 @@
         <v>6342234191</v>
       </c>
       <c r="D290" s="5" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="E290" s="3"/>
     </row>
@@ -6400,7 +6422,7 @@
         <v>6055490417</v>
       </c>
       <c r="D291" s="3" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E291" s="3"/>
     </row>
@@ -6415,7 +6437,7 @@
         <v>5048920859</v>
       </c>
       <c r="D292" s="5" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="E292" s="3"/>
     </row>
@@ -6430,7 +6452,7 @@
         <v>8316196500</v>
       </c>
       <c r="D293" s="3" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="E293" s="3"/>
     </row>
@@ -6445,7 +6467,7 @@
         <v>8723838363</v>
       </c>
       <c r="D294" s="5" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="E294" s="3"/>
     </row>
@@ -6460,7 +6482,7 @@
         <v>9513446363</v>
       </c>
       <c r="D295" s="5" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="E295" s="3"/>
     </row>
@@ -6475,7 +6497,7 @@
         <v>5493250169</v>
       </c>
       <c r="D296" s="3" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="E296" s="3"/>
     </row>
@@ -6490,7 +6512,7 @@
         <v>6685817155</v>
       </c>
       <c r="D297" s="3" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="E297" s="3"/>
     </row>
@@ -6505,7 +6527,7 @@
         <v>6509946997</v>
       </c>
       <c r="D298" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="E298" s="3"/>
     </row>
@@ -6520,7 +6542,7 @@
         <v>6626267250</v>
       </c>
       <c r="D299" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="E299" s="3"/>
     </row>
@@ -6535,7 +6557,7 @@
         <v>7611183433</v>
       </c>
       <c r="D300" s="5" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="E300" s="3"/>
     </row>
@@ -6550,7 +6572,7 @@
         <v>9185954912</v>
       </c>
       <c r="D301" s="5" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="E301" s="3"/>
     </row>
@@ -6565,7 +6587,7 @@
         <v>7694619371</v>
       </c>
       <c r="D302" s="3" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E302" s="3"/>
     </row>
@@ -6580,7 +6602,7 @@
         <v>7720684000</v>
       </c>
       <c r="D303" s="3" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="E303" s="3"/>
     </row>
@@ -6595,7 +6617,7 @@
         <v>8976291857</v>
       </c>
       <c r="D304" s="5" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="E304" s="3"/>
     </row>
@@ -6610,7 +6632,7 @@
         <v>7865931792</v>
       </c>
       <c r="D305" s="3" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="E305" s="3"/>
     </row>
@@ -6625,7 +6647,7 @@
         <v>8721527776</v>
       </c>
       <c r="D306" s="5" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="E306" s="3"/>
     </row>
@@ -6640,7 +6662,7 @@
         <v>8349565324</v>
       </c>
       <c r="D307" s="5" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="E307" s="3"/>
     </row>
@@ -6655,7 +6677,7 @@
         <v>8797360748</v>
       </c>
       <c r="D308" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="E308" s="3"/>
     </row>
@@ -6670,7 +6692,7 @@
         <v>8405084468</v>
       </c>
       <c r="D309" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="E309" s="3"/>
     </row>
@@ -6685,7 +6707,7 @@
         <v>9007222503</v>
       </c>
       <c r="D310" s="5" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="E310" s="3"/>
     </row>
@@ -6700,7 +6722,7 @@
         <v>8250354626</v>
       </c>
       <c r="D311" s="5" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="E311" s="3"/>
     </row>
@@ -6715,7 +6737,7 @@
         <v>8815932963</v>
       </c>
       <c r="D312" s="5" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="E312" s="3"/>
     </row>
@@ -6730,7 +6752,7 @@
         <v>1980313759</v>
       </c>
       <c r="D313" s="5" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="E313" s="3"/>
     </row>
@@ -6745,7 +6767,7 @@
         <v>8700495894</v>
       </c>
       <c r="D314" s="5" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="E314" s="3"/>
     </row>
@@ -6760,7 +6782,7 @@
         <v>8983113712</v>
       </c>
       <c r="D315" s="3" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="E315" s="3"/>
     </row>
@@ -6775,7 +6797,7 @@
         <v>7412562123</v>
       </c>
       <c r="D316" s="5" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="E316" s="3"/>
     </row>
@@ -6790,7 +6812,7 @@
         <v>8032769325</v>
       </c>
       <c r="D317" s="5" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="E317" s="3"/>
     </row>
@@ -6805,7 +6827,7 @@
         <v>8466167023</v>
       </c>
       <c r="D318" s="5" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="E318" s="3"/>
     </row>
@@ -6820,7 +6842,7 @@
         <v>8984729970</v>
       </c>
       <c r="D319" s="5" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="E319" s="3"/>
     </row>
@@ -6835,7 +6857,7 @@
         <v>8887701336</v>
       </c>
       <c r="D320" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="E320" s="3"/>
     </row>
@@ -6850,7 +6872,7 @@
         <v>9131604249</v>
       </c>
       <c r="D321" s="5" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="E321" s="3"/>
     </row>
@@ -6865,7 +6887,7 @@
         <v>9131604249</v>
       </c>
       <c r="D322" s="5" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E322" s="3"/>
     </row>
@@ -6880,7 +6902,7 @@
         <v>9131604249</v>
       </c>
       <c r="D323" s="5" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="E323" s="3"/>
     </row>
@@ -6895,7 +6917,7 @@
         <v>8399098479</v>
       </c>
       <c r="D324" s="5" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="E324" s="3"/>
     </row>
@@ -6910,7 +6932,7 @@
         <v>8399098479</v>
       </c>
       <c r="D325" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="E325" s="3"/>
     </row>
@@ -6925,7 +6947,7 @@
         <v>8386057039</v>
       </c>
       <c r="D326" s="5" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="E326" s="3"/>
     </row>
@@ -6940,7 +6962,7 @@
         <v>39488821</v>
       </c>
       <c r="D327" s="5" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="E327" s="3"/>
     </row>
@@ -6955,7 +6977,7 @@
         <v>39488823</v>
       </c>
       <c r="D328" s="5" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="E328" s="3"/>
     </row>
@@ -6970,7 +6992,7 @@
         <v>7550728226</v>
       </c>
       <c r="D329" s="5" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="E329" s="3"/>
     </row>
@@ -6985,7 +7007,7 @@
         <v>7550728226</v>
       </c>
       <c r="D330" s="5" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="E330" s="3"/>
     </row>
@@ -7000,7 +7022,7 @@
         <v>7561041028</v>
       </c>
       <c r="D331" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="E331" s="3"/>
     </row>
@@ -7015,7 +7037,7 @@
         <v>7575479902</v>
       </c>
       <c r="D332" s="5" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="E332" s="3"/>
     </row>
@@ -7030,7 +7052,7 @@
         <v>7567547367</v>
       </c>
       <c r="D333" s="5" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E333" s="3"/>
     </row>
@@ -7045,7 +7067,7 @@
         <v>8441795411</v>
       </c>
       <c r="D334" s="5" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E334" s="3"/>
     </row>
@@ -7060,7 +7082,7 @@
         <v>7561407336</v>
       </c>
       <c r="D335" s="3" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="E335" s="3"/>
     </row>
@@ -7075,7 +7097,7 @@
         <v>153446388</v>
       </c>
       <c r="D336" s="5" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="E336" s="3"/>
     </row>
@@ -7090,7 +7112,7 @@
         <v>39488818</v>
       </c>
       <c r="D337" s="5" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="E337" s="3"/>
     </row>
@@ -7105,7 +7127,7 @@
         <v>2227858529</v>
       </c>
       <c r="D338" s="5" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="E338" s="3"/>
     </row>
@@ -7120,7 +7142,7 @@
         <v>2227974674</v>
       </c>
       <c r="D339" s="5" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="E339" s="3"/>
     </row>
@@ -7135,7 +7157,7 @@
         <v>6138990380</v>
       </c>
       <c r="D340" s="3" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="E340" s="3"/>
     </row>
@@ -7150,7 +7172,7 @@
         <v>6853835673</v>
       </c>
       <c r="D341" s="5" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="E341" s="3"/>
     </row>
@@ -7165,7 +7187,7 @@
         <v>2176223537</v>
       </c>
       <c r="D342" s="3" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="E342" s="3"/>
     </row>
@@ -7180,7 +7202,7 @@
         <v>7610690083</v>
       </c>
       <c r="D343" s="3" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="E343" s="3"/>
     </row>
@@ -7195,7 +7217,7 @@
         <v>8423126898</v>
       </c>
       <c r="D344" s="5" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="E344" s="3"/>
     </row>
@@ -7210,7 +7232,7 @@
         <v>8389915227</v>
       </c>
       <c r="D345" s="5" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="E345" s="3"/>
     </row>
@@ -7225,7 +7247,7 @@
         <v>6297170783</v>
       </c>
       <c r="D346" s="3" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="E346" s="3"/>
     </row>
@@ -7240,7 +7262,7 @@
         <v>7750278395</v>
       </c>
       <c r="D347" s="5" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="E347" s="3"/>
     </row>
@@ -7255,7 +7277,7 @@
         <v>7551636407</v>
       </c>
       <c r="D348" s="5" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E348" s="3"/>
     </row>
@@ -7270,7 +7292,7 @@
         <v>7623031098</v>
       </c>
       <c r="D349" s="5" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="E349" s="3"/>
     </row>
@@ -7285,7 +7307,7 @@
         <v>9131611382</v>
       </c>
       <c r="D350" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="E350" s="3"/>
     </row>
@@ -7300,7 +7322,7 @@
         <v>7694347683</v>
       </c>
       <c r="D351" s="3" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="E351" s="3"/>
     </row>
@@ -7315,7 +7337,7 @@
         <v>6214916365</v>
       </c>
       <c r="D352" s="5" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="E352" s="3"/>
     </row>
@@ -7330,7 +7352,7 @@
         <v>9102032882</v>
       </c>
       <c r="D353" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="E353" s="3"/>
     </row>
@@ -7345,7 +7367,7 @@
         <v>9115653414</v>
       </c>
       <c r="D354" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E354" s="3"/>
     </row>
@@ -7360,7 +7382,7 @@
         <v>9221400246</v>
       </c>
       <c r="D355" s="5" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="E355" s="3"/>
     </row>
@@ -7375,7 +7397,7 @@
         <v>7563544764</v>
       </c>
       <c r="D356" s="3" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="E356" s="3"/>
     </row>
@@ -7390,7 +7412,7 @@
         <v>8422778137</v>
       </c>
       <c r="D357" s="5" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="E357" s="3"/>
     </row>
@@ -7405,7 +7427,7 @@
         <v>9192238440</v>
       </c>
       <c r="D358" s="5" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E358" s="3"/>
     </row>
@@ -7420,7 +7442,7 @@
         <v>9192238440</v>
       </c>
       <c r="D359" s="5" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="E359" s="3"/>
     </row>
@@ -7435,7 +7457,7 @@
         <v>7576301717</v>
       </c>
       <c r="D360" s="5" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="E360" s="3"/>
     </row>
@@ -7450,7 +7472,7 @@
         <v>8425098701</v>
       </c>
       <c r="D361" s="5" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="E361" s="3"/>
     </row>
@@ -7465,7 +7487,7 @@
         <v>8425098701</v>
       </c>
       <c r="D362" s="5" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="E362" s="3"/>
     </row>
@@ -7480,7 +7502,7 @@
         <v>8425098701</v>
       </c>
       <c r="D363" s="5" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="E363" s="3"/>
     </row>
@@ -7495,7 +7517,7 @@
         <v>6854394591</v>
       </c>
       <c r="D364" s="5" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="E364" s="3"/>
     </row>
@@ -7510,7 +7532,7 @@
         <v>6854394591</v>
       </c>
       <c r="D365" s="5" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E365" s="3"/>
     </row>
@@ -7525,7 +7547,7 @@
         <v>339982697</v>
       </c>
       <c r="D366" s="5" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="E366" s="3"/>
     </row>
@@ -7540,7 +7562,7 @@
         <v>339982697</v>
       </c>
       <c r="D367" s="5" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E367" s="3"/>
     </row>
@@ -7555,7 +7577,7 @@
         <v>7689191114</v>
       </c>
       <c r="D368" s="5" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="E368" s="3"/>
     </row>
@@ -7570,7 +7592,7 @@
         <v>8539985041</v>
       </c>
       <c r="D369" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="E369" s="3"/>
     </row>
@@ -7585,7 +7607,7 @@
         <v>9122066394</v>
       </c>
       <c r="D370" s="5" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E370" s="3"/>
     </row>
@@ -7600,7 +7622,7 @@
         <v>9122081331</v>
       </c>
       <c r="D371" s="5" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="E371" s="3"/>
     </row>
@@ -7615,7 +7637,7 @@
         <v>9171387066</v>
       </c>
       <c r="D372" s="5" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="E372" s="3"/>
     </row>
@@ -7630,7 +7652,7 @@
         <v>1649937793</v>
       </c>
       <c r="D373" s="3" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="E373" s="3"/>
     </row>
@@ -7645,7 +7667,7 @@
         <v>8104048795</v>
       </c>
       <c r="D374" s="3" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="E374" s="3"/>
     </row>
@@ -7660,7 +7682,7 @@
         <v>5493723022</v>
       </c>
       <c r="D375" s="3" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="E375" s="3"/>
     </row>
@@ -7675,7 +7697,7 @@
         <v>7554201576</v>
       </c>
       <c r="D376" s="5" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="E376" s="3"/>
     </row>
@@ -7690,7 +7712,7 @@
         <v>8885638632</v>
       </c>
       <c r="D377" s="3" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="E377" s="3"/>
     </row>
@@ -7705,7 +7727,7 @@
         <v>8885638632</v>
       </c>
       <c r="D378" s="5" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="E378" s="3"/>
     </row>
@@ -7720,7 +7742,7 @@
         <v>7544203621</v>
       </c>
       <c r="D379" s="5" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="E379" s="3"/>
     </row>
@@ -7735,7 +7757,7 @@
         <v>8774118699</v>
       </c>
       <c r="D380" s="5" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="E380" s="3"/>
     </row>
@@ -7750,7 +7772,7 @@
         <v>6682869338</v>
       </c>
       <c r="D381" s="5" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="E381" s="3"/>
     </row>
@@ -7765,7 +7787,7 @@
         <v>6682869338</v>
       </c>
       <c r="D382" s="5" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="E382" s="3"/>
     </row>
@@ -7780,7 +7802,7 @@
         <v>9531671822</v>
       </c>
       <c r="D383" s="5" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="E383" s="3"/>
     </row>
@@ -7795,7 +7817,7 @@
         <v>9531671825</v>
       </c>
       <c r="D384" s="5" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="E384" s="3"/>
     </row>
@@ -7810,7 +7832,7 @@
         <v>8605189784</v>
       </c>
       <c r="D385" s="5" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="E385" s="3"/>
     </row>
@@ -7825,7 +7847,7 @@
         <v>7561344594</v>
       </c>
       <c r="D386" s="5" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="E386" s="3"/>
     </row>
@@ -7840,7 +7862,7 @@
         <v>7561344594</v>
       </c>
       <c r="D387" s="5" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="E387" s="3"/>
     </row>
@@ -7855,7 +7877,7 @@
         <v>7561344594</v>
       </c>
       <c r="D388" s="5" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="E388" s="3"/>
     </row>
@@ -7870,7 +7892,7 @@
         <v>7561437551</v>
       </c>
       <c r="D389" s="5" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E389" s="3"/>
     </row>
@@ -7885,7 +7907,7 @@
         <v>8351238275</v>
       </c>
       <c r="D390" s="5" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="E390" s="3"/>
     </row>
@@ -7900,7 +7922,7 @@
         <v>9036675167</v>
       </c>
       <c r="D391" s="5" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="E391" s="3"/>
     </row>
@@ -7915,7 +7937,7 @@
         <v>9400128676</v>
       </c>
       <c r="D392" s="5" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="E392" s="3"/>
     </row>
@@ -7930,7 +7952,7 @@
         <v>8411418022</v>
       </c>
       <c r="D393" s="3" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="E393" s="3"/>
     </row>
@@ -7945,7 +7967,7 @@
         <v>9042243132</v>
       </c>
       <c r="D394" s="5" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="E394" s="3"/>
     </row>
@@ -7960,7 +7982,7 @@
         <v>9042243132</v>
       </c>
       <c r="D395" s="5" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="E395" s="3"/>
     </row>
@@ -7975,7 +7997,7 @@
         <v>9042243132</v>
       </c>
       <c r="D396" s="5" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="E396" s="3"/>
     </row>
@@ -7990,7 +8012,7 @@
         <v>8797331961</v>
       </c>
       <c r="D397" s="5" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="E397" s="3"/>
     </row>
@@ -8005,7 +8027,7 @@
         <v>6597496123</v>
       </c>
       <c r="D398" s="5" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="E398" s="3"/>
     </row>
@@ -8020,7 +8042,7 @@
         <v>6597496123</v>
       </c>
       <c r="D399" s="5" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="E399" s="3"/>
     </row>
@@ -8035,7 +8057,7 @@
         <v>6597496123</v>
       </c>
       <c r="D400" s="5" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="E400" s="3"/>
     </row>
@@ -8050,7 +8072,7 @@
         <v>9312501151</v>
       </c>
       <c r="D401" s="5" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="E401" s="3"/>
     </row>
@@ -8065,7 +8087,7 @@
         <v>9068448045</v>
       </c>
       <c r="D402" s="5" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="E402" s="3"/>
     </row>
@@ -8080,7 +8102,7 @@
         <v>9068448045</v>
       </c>
       <c r="D403" s="5" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="E403" s="3"/>
     </row>
@@ -8095,7 +8117,7 @@
         <v>9069436024</v>
       </c>
       <c r="D404" s="5" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="E404" s="3"/>
     </row>
@@ -8110,7 +8132,7 @@
         <v>9180860970</v>
       </c>
       <c r="D405" s="5" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="E405" s="3"/>
     </row>
@@ -8125,7 +8147,7 @@
         <v>9180860970</v>
       </c>
       <c r="D406" s="5" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="E406" s="3"/>
     </row>
@@ -8140,7 +8162,7 @@
         <v>9180860970</v>
       </c>
       <c r="D407" s="5" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="E407" s="3"/>
     </row>
@@ -8155,7 +8177,7 @@
         <v>7544195195</v>
       </c>
       <c r="D408" s="5" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="E408" s="3"/>
     </row>
@@ -8170,7 +8192,7 @@
         <v>7314835858</v>
       </c>
       <c r="D409" s="5" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="E409" s="3"/>
     </row>
@@ -8185,7 +8207,7 @@
         <v>7294578866</v>
       </c>
       <c r="D410" s="5" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="E410" s="3"/>
     </row>
@@ -8200,7 +8222,7 @@
         <v>8542993826</v>
       </c>
       <c r="D411" s="5" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="E411" s="3"/>
     </row>
@@ -8215,7 +8237,7 @@
         <v>1792472152</v>
       </c>
       <c r="D412" s="3" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="E412" s="3"/>
     </row>
@@ -8230,7 +8252,7 @@
         <v>8579716988</v>
       </c>
       <c r="D413" s="5" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="E413" s="3"/>
     </row>
@@ -8245,7 +8267,7 @@
         <v>8579716988</v>
       </c>
       <c r="D414" s="5" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="E414" s="3"/>
     </row>
@@ -8260,7 +8282,7 @@
         <v>8653413648</v>
       </c>
       <c r="D415" s="5" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="E415" s="3"/>
     </row>
@@ -8275,7 +8297,7 @@
         <v>8736301959</v>
       </c>
       <c r="D416" s="5" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="E416" s="3"/>
     </row>
@@ -8290,7 +8312,7 @@
         <v>2106612139</v>
       </c>
       <c r="D417" s="5" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="E417" s="3"/>
     </row>
@@ -8305,7 +8327,7 @@
         <v>8769637100</v>
       </c>
       <c r="D418" s="5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="E418" s="3"/>
     </row>
@@ -8320,7 +8342,7 @@
         <v>5938569723</v>
       </c>
       <c r="D419" s="5" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="E419" s="3"/>
     </row>
@@ -8335,7 +8357,7 @@
         <v>7266373878</v>
       </c>
       <c r="D420" s="3" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="E420" s="3"/>
     </row>
@@ -8350,7 +8372,7 @@
         <v>6636872479</v>
       </c>
       <c r="D421" s="3" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="E421" s="3"/>
     </row>
@@ -8365,7 +8387,7 @@
         <v>7503792000</v>
       </c>
       <c r="D422" s="5" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="E422" s="3"/>
     </row>
@@ -8380,7 +8402,7 @@
         <v>9293810504</v>
       </c>
       <c r="D423" s="5" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="E423" s="3"/>
     </row>
@@ -8395,7 +8417,7 @@
         <v>8472184647</v>
       </c>
       <c r="D424" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E424" s="3"/>
     </row>
@@ -8410,7 +8432,7 @@
         <v>2106560460</v>
       </c>
       <c r="D425" s="3" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="E425" s="3"/>
     </row>
@@ -8425,7 +8447,7 @@
         <v>9158117948</v>
       </c>
       <c r="D426" s="5" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="E426" s="3"/>
     </row>
@@ -8440,7 +8462,7 @@
         <v>9158117948</v>
       </c>
       <c r="D427" s="5" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="E427" s="3"/>
     </row>
@@ -8455,7 +8477,7 @@
         <v>9158117948</v>
       </c>
       <c r="D428" s="5" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E428" s="3"/>
     </row>
@@ -8470,7 +8492,7 @@
         <v>8409324207</v>
       </c>
       <c r="D429" s="5" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="E429" s="3"/>
     </row>
@@ -8485,7 +8507,7 @@
         <v>8409324207</v>
       </c>
       <c r="D430" s="5" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="E430" s="3"/>
     </row>
@@ -8500,7 +8522,7 @@
         <v>9262753546</v>
       </c>
       <c r="D431" s="5" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="E431" s="3"/>
     </row>
@@ -8515,7 +8537,7 @@
         <v>8834968166</v>
       </c>
       <c r="D432" s="5" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E432" s="3"/>
     </row>
@@ -8530,7 +8552,7 @@
         <v>8722009358</v>
       </c>
       <c r="D433" s="5" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E433" s="3"/>
     </row>
@@ -8545,7 +8567,7 @@
         <v>8440420865</v>
       </c>
       <c r="D434" s="5" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="E434" s="3"/>
     </row>
@@ -8560,7 +8582,7 @@
         <v>8708381506</v>
       </c>
       <c r="D435" s="5" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="E435" s="3"/>
     </row>
@@ -8575,7 +8597,7 @@
         <v>8708381506</v>
       </c>
       <c r="D436" s="5" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="E436" s="3"/>
     </row>
@@ -8590,7 +8612,7 @@
         <v>9146170961</v>
       </c>
       <c r="D437" s="5" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="E437" s="3"/>
     </row>
@@ -8605,7 +8627,7 @@
         <v>9146170961</v>
       </c>
       <c r="D438" s="5" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="E438" s="3"/>
     </row>
@@ -8620,7 +8642,7 @@
         <v>9422443778</v>
       </c>
       <c r="D439" s="5" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E439" s="3"/>
     </row>
@@ -8635,7 +8657,7 @@
         <v>9422443778</v>
       </c>
       <c r="D440" s="5" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="E440" s="3"/>
     </row>
@@ -8650,7 +8672,7 @@
         <v>7865904123</v>
       </c>
       <c r="D441" s="5" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="E441" s="3"/>
     </row>
@@ -8665,7 +8687,7 @@
         <v>7865904123</v>
       </c>
       <c r="D442" s="5" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="E442" s="3"/>
     </row>
@@ -8680,7 +8702,7 @@
         <v>7825521878</v>
       </c>
       <c r="D443" s="3" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E443" s="3"/>
     </row>
@@ -8695,7 +8717,7 @@
         <v>7883641133</v>
       </c>
       <c r="D444" s="5" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E444" s="3"/>
     </row>
@@ -8710,7 +8732,7 @@
         <v>7458576120</v>
       </c>
       <c r="D445" s="5" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="E445" s="3"/>
     </row>
@@ -8725,7 +8747,7 @@
         <v>7043556197</v>
       </c>
       <c r="D446" s="5" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E446" s="3"/>
     </row>
@@ -8740,7 +8762,7 @@
         <v>7352904351</v>
       </c>
       <c r="D447" s="5" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="E447" s="3"/>
     </row>
@@ -8755,7 +8777,7 @@
         <v>8921470415</v>
       </c>
       <c r="D448" s="5" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="E448" s="3"/>
     </row>
@@ -8770,7 +8792,7 @@
         <v>8918314315</v>
       </c>
       <c r="D449" s="5" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="E449" s="3"/>
     </row>
@@ -8785,7 +8807,7 @@
         <v>9239467730</v>
       </c>
       <c r="D450" s="5" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="E450" s="3"/>
     </row>
@@ -8800,7 +8822,7 @@
         <v>8284261333</v>
       </c>
       <c r="D451" s="5" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="E451" s="3"/>
     </row>
@@ -8815,7 +8837,7 @@
         <v>224865338</v>
       </c>
       <c r="D452" s="5" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="E452" s="3"/>
     </row>
@@ -8830,7 +8852,7 @@
         <v>2160218428</v>
       </c>
       <c r="D453" s="3" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="E453" s="3"/>
     </row>
@@ -8845,7 +8867,7 @@
         <v>2070424740</v>
       </c>
       <c r="D454" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="E454" s="3"/>
     </row>
@@ -8860,7 +8882,7 @@
         <v>7598271263</v>
       </c>
       <c r="D455" s="3" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="E455" s="3"/>
     </row>
@@ -8875,7 +8897,7 @@
         <v>7606163668</v>
       </c>
       <c r="D456" s="5" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="E456" s="3"/>
     </row>
@@ -8890,7 +8912,7 @@
         <v>8448202877</v>
       </c>
       <c r="D457" s="5" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="E457" s="3"/>
     </row>
@@ -8905,7 +8927,7 @@
         <v>7595404561</v>
       </c>
       <c r="D458" s="5" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="E458" s="3"/>
     </row>
@@ -8920,7 +8942,7 @@
         <v>5601771215</v>
       </c>
       <c r="D459" s="5" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="E459" s="3"/>
     </row>
@@ -8935,7 +8957,7 @@
         <v>6249025659</v>
       </c>
       <c r="D460" s="5" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="E460" s="3"/>
     </row>
@@ -8950,7 +8972,7 @@
         <v>7650029022</v>
       </c>
       <c r="D461" s="5" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="E461" s="3"/>
     </row>
@@ -8965,7 +8987,7 @@
         <v>4382661</v>
       </c>
       <c r="D462" s="5" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="E462" s="3"/>
     </row>
@@ -8980,7 +9002,7 @@
         <v>4382661</v>
       </c>
       <c r="D463" s="5" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="E463" s="3"/>
     </row>
@@ -8995,7 +9017,7 @@
         <v>4382661</v>
       </c>
       <c r="D464" s="5" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="E464" s="3"/>
     </row>
@@ -9010,7 +9032,7 @@
         <v>8647726277</v>
       </c>
       <c r="D465" s="5" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="E465" s="3"/>
     </row>
@@ -9025,7 +9047,7 @@
         <v>7560734129</v>
       </c>
       <c r="D466" s="5" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E466" s="3"/>
     </row>
@@ -9040,7 +9062,7 @@
         <v>7732557202</v>
       </c>
       <c r="D467" s="5" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="E467" s="3"/>
     </row>
@@ -9055,7 +9077,7 @@
         <v>8463160132</v>
       </c>
       <c r="D468" s="5" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="E468" s="3"/>
     </row>
@@ -9070,7 +9092,7 @@
         <v>7934862378</v>
       </c>
       <c r="D469" s="5" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="E469" s="3"/>
     </row>
@@ -9085,7 +9107,7 @@
         <v>8403153859</v>
       </c>
       <c r="D470" s="5" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="E470" s="3"/>
     </row>
@@ -9100,7 +9122,7 @@
         <v>1915911330</v>
       </c>
       <c r="D471" s="5" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="E471" s="3"/>
     </row>
@@ -9115,7 +9137,7 @@
         <v>1516177491</v>
       </c>
       <c r="D472" s="5" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="E472" s="3"/>
     </row>
@@ -9130,7 +9152,7 @@
         <v>4745192130</v>
       </c>
       <c r="D473" s="5" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="E473" s="3"/>
     </row>
@@ -9145,7 +9167,7 @@
         <v>4847970517</v>
       </c>
       <c r="D474" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E474" s="3"/>
     </row>
@@ -9160,7 +9182,7 @@
         <v>4847970517</v>
       </c>
       <c r="D475" s="5" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="E475" s="3"/>
     </row>
@@ -9175,7 +9197,7 @@
         <v>4745192130</v>
       </c>
       <c r="D476" s="5" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="E476" s="3"/>
     </row>
@@ -9190,7 +9212,7 @@
         <v>9447895346</v>
       </c>
       <c r="D477" s="5" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="E477" s="3"/>
     </row>
@@ -9205,7 +9227,7 @@
         <v>1234244311</v>
       </c>
       <c r="D478" s="5" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="E478" s="3"/>
     </row>
@@ -9220,7 +9242,7 @@
         <v>5491212604</v>
       </c>
       <c r="D479" s="5" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="E479" s="3"/>
     </row>
@@ -9235,7 +9257,7 @@
         <v>1731644048</v>
       </c>
       <c r="D480" s="5" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="E480" s="3"/>
     </row>
@@ -9250,7 +9272,7 @@
         <v>1234244350</v>
       </c>
       <c r="D481" s="5" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="E481" s="3"/>
     </row>
@@ -9265,7 +9287,7 @@
         <v>1654777941</v>
       </c>
       <c r="D482" s="5" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="E482" s="3"/>
     </row>
@@ -9280,7 +9302,7 @@
         <v>1654793049</v>
       </c>
       <c r="D483" s="5" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="E483" s="3"/>
     </row>
@@ -9295,7 +9317,7 @@
         <v>1234244291</v>
       </c>
       <c r="D484" s="5" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="E484" s="3"/>
     </row>
@@ -9310,7 +9332,7 @@
         <v>5960306639</v>
       </c>
       <c r="D485" s="5" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="E485" s="3"/>
     </row>
@@ -9325,7 +9347,7 @@
         <v>7650792362</v>
       </c>
       <c r="D486" s="5" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="E486" s="3"/>
     </row>
@@ -9340,7 +9362,7 @@
         <v>5600455899</v>
       </c>
       <c r="D487" s="5" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="E487" s="3"/>
     </row>
@@ -9355,7 +9377,7 @@
         <v>8231916739</v>
       </c>
       <c r="D488" s="5" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="E488" s="3"/>
     </row>
@@ -9370,7 +9392,7 @@
         <v>5498573390</v>
       </c>
       <c r="D489" s="5" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="E489" s="3"/>
     </row>
@@ -9385,7 +9407,7 @@
         <v>2032552954</v>
       </c>
       <c r="D490" s="5" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="E490" s="3"/>
     </row>
@@ -9400,7 +9422,7 @@
         <v>7515968701</v>
       </c>
       <c r="D491" s="5" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="E491" s="3"/>
     </row>
@@ -9415,7 +9437,7 @@
         <v>4971171973</v>
       </c>
       <c r="D492" s="5" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="E492" s="3"/>
     </row>
@@ -9430,7 +9452,7 @@
         <v>5449445963</v>
       </c>
       <c r="D493" s="5" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E493" s="3"/>
     </row>
@@ -9445,7 +9467,7 @@
         <v>1255415728</v>
       </c>
       <c r="D494" s="5" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="E494" s="3"/>
     </row>
@@ -9460,7 +9482,7 @@
         <v>8334316521</v>
       </c>
       <c r="D495" s="5" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="E495" s="3"/>
     </row>
@@ -9475,7 +9497,7 @@
         <v>6341825694</v>
       </c>
       <c r="D496" s="5" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="E496" s="3"/>
     </row>
@@ -9490,7 +9512,7 @@
         <v>7597292554</v>
       </c>
       <c r="D497" s="5" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="E497" s="3"/>
     </row>
@@ -9505,7 +9527,7 @@
         <v>6565885970</v>
       </c>
       <c r="D498" s="5" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="E498" s="3"/>
     </row>
@@ -9520,7 +9542,7 @@
         <v>8386152066</v>
       </c>
       <c r="D499" s="5" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="E499" s="3"/>
     </row>
@@ -9535,7 +9557,7 @@
         <v>8422687942</v>
       </c>
       <c r="D500" s="5" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="E500" s="3"/>
     </row>
@@ -9550,7 +9572,7 @@
         <v>8520332333</v>
       </c>
       <c r="D501" s="3" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="E501" s="3"/>
     </row>
@@ -9565,7 +9587,7 @@
         <v>5497202248</v>
       </c>
       <c r="D502" s="5" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="E502" s="3"/>
     </row>
@@ -9580,7 +9602,7 @@
         <v>7107526564</v>
       </c>
       <c r="D503" s="5" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="E503" s="3"/>
     </row>
@@ -9595,7 +9617,7 @@
         <v>7351124166</v>
       </c>
       <c r="D504" s="3" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="E504" s="3"/>
     </row>
@@ -9610,7 +9632,7 @@
         <v>5815984652</v>
       </c>
       <c r="D505" s="5" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="E505" s="3"/>
     </row>
@@ -9625,7 +9647,7 @@
         <v>8550437968</v>
       </c>
       <c r="D506" s="5" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="E506" s="3"/>
     </row>
@@ -9640,7 +9662,7 @@
         <v>8487691454</v>
       </c>
       <c r="D507" s="5" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="E507" s="3"/>
     </row>
@@ -9655,7 +9677,7 @@
         <v>8394671369</v>
       </c>
       <c r="D508" s="5" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="E508" s="3"/>
     </row>
@@ -9670,7 +9692,7 @@
         <v>8540043494</v>
       </c>
       <c r="D509" s="5" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="E509" s="3"/>
     </row>
@@ -9685,7 +9707,7 @@
         <v>8550269015</v>
       </c>
       <c r="D510" s="5" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="E510" s="3"/>
     </row>
@@ -9700,7 +9722,7 @@
         <v>9557521114</v>
       </c>
       <c r="D511" s="5" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="E511" s="3"/>
     </row>
@@ -9715,7 +9737,7 @@
         <v>9557521114</v>
       </c>
       <c r="D512" s="5" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="E512" s="3"/>
     </row>
@@ -9730,7 +9752,7 @@
         <v>9557521114</v>
       </c>
       <c r="D513" s="5" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="E513" s="3"/>
     </row>
@@ -9745,7 +9767,7 @@
         <v>9557446889</v>
       </c>
       <c r="D514" s="5" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="E514" s="3"/>
     </row>
@@ -9760,7 +9782,7 @@
         <v>9557446889</v>
       </c>
       <c r="D515" s="5" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="E515" s="3"/>
     </row>
@@ -9775,7 +9797,7 @@
         <v>1519776763</v>
       </c>
       <c r="D516" s="5" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="E516" s="3"/>
     </row>
@@ -9790,7 +9812,7 @@
         <v>9542122109</v>
       </c>
       <c r="D517" s="5" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="E517" s="3"/>
     </row>
@@ -9805,7 +9827,7 @@
         <v>1519776763</v>
       </c>
       <c r="D518" s="5" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="E518" s="3"/>
     </row>
@@ -9820,7 +9842,7 @@
         <v>9591319894</v>
       </c>
       <c r="D519" s="5" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="E519" s="3"/>
     </row>
@@ -9835,7 +9857,7 @@
         <v>9591319894</v>
       </c>
       <c r="D520" s="5" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="E520" s="3"/>
     </row>
@@ -9850,7 +9872,7 @@
         <v>9599420140</v>
       </c>
       <c r="D521" s="5" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="E521" s="3"/>
     </row>
@@ -9865,7 +9887,7 @@
         <v>9579352104</v>
       </c>
       <c r="D522" s="5" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="E522" s="3"/>
     </row>
@@ -9880,7 +9902,7 @@
         <v>9593439241</v>
       </c>
       <c r="D523" s="5" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="E523" s="3"/>
     </row>
@@ -9895,7 +9917,7 @@
         <v>8409324207</v>
       </c>
       <c r="D524" s="5" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="E524" s="3"/>
     </row>
@@ -9910,7 +9932,7 @@
         <v>9584901273</v>
       </c>
       <c r="D525" s="5" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="E525" s="3"/>
     </row>
@@ -9925,7 +9947,7 @@
         <v>9640499462</v>
       </c>
       <c r="D526" s="5" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="E526" s="3"/>
     </row>
@@ -9940,7 +9962,7 @@
         <v>9644116866</v>
       </c>
       <c r="D527" s="3" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="E527" s="3"/>
     </row>
@@ -9955,7 +9977,7 @@
         <v>9644116866</v>
       </c>
       <c r="D528" s="3" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="E528" s="3"/>
     </row>
@@ -9970,7 +9992,7 @@
         <v>9644097189</v>
       </c>
       <c r="D529" s="3" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="E529" s="3"/>
     </row>
@@ -9985,7 +10007,7 @@
         <v>9644097189</v>
       </c>
       <c r="D530" s="5" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="E530" s="3"/>
     </row>
@@ -10000,7 +10022,7 @@
         <v>9649976775</v>
       </c>
       <c r="D531" s="5" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="E531" s="3"/>
     </row>
@@ -10015,7 +10037,7 @@
         <v>9678595695</v>
       </c>
       <c r="D532" s="5" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="E532" s="3"/>
     </row>
@@ -10030,7 +10052,7 @@
         <v>9678595695</v>
       </c>
       <c r="D533" s="5" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="E533" s="3"/>
     </row>
